--- a/physician_forms/001_new_patient_enrollment_form--physician_forms.xlsx
+++ b/physician_forms/001_new_patient_enrollment_form--physician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Emergency First Name</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Emergency Last Name</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Emergency Phone</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Emergency Email</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mother</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>father</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Partner</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>spouse</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Child</t>
         </is>
       </c>
     </row>
@@ -1233,44 +1233,10 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>parent</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
-        <is>
-          <t>Parent</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>emergency_relation_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>child</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Child</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>emergency_relation_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
